--- a/data/trans_orig/IP1018-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1018-Provincia-trans_orig.xlsx
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67679</t>
+          <t>66635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135276</t>
+          <t>135054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125013</t>
+          <t>125016</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130746</t>
+          <t>130517</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258598</t>
+          <t>257999</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>263598</t>
+          <t>263599</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154623</t>
+          <t>154271</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318425</t>
+          <t>318044</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>676287</t>
+          <t>676184</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>717242</t>
+          <t>717804</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1396479</t>
+          <t>1396145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402480</t>
+          <t>1402521</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>53684</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59115</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115224</t>
+          <t>115590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121244</t>
+          <t>121245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100427</t>
+          <t>100571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210986</t>
+          <t>210625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167880</t>
+          <t>167884</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331607</t>
+          <t>332079</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>698947</t>
+          <t>698850</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>703789</t>
+          <t>703788</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>739343</t>
+          <t>739256</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1441262</t>
+          <t>1440989</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1448037</t>
+          <t>1448022</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP1018-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1018-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -840,42 +840,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1178,47 +1178,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>525</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3692</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2622</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2870</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69802</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67681</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69802</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66635</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135054</t>
+          <t>135302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4253</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3606</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4085</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1398</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5138</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>134257</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>131402</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>127902</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>125016</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>124537</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,44%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>134257</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>130517</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>380</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>257999</t>
+          <t>258681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>263599</t>
+          <t>263598</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,72 +3123,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3633</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157250</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>154271</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>154639</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>493</t>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318044</t>
+          <t>318033</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5757</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4837</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4869</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>4896</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>720777</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>716943</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>722175</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,93%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>679647</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>676184</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>676152</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>720777</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>717804</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>722177</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,93%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2099</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1396145</t>
+          <t>1396244</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402521</t>
+          <t>1403000</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4158,47 +4158,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4501,47 +4501,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4844,47 +4844,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5187,47 +5187,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5873,47 +5873,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6216,47 +6216,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6559,47 +6559,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6902,47 +6902,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7368,72 +7368,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4922</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1221</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3687</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4283</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -7486,69 +7486,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>63374</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59540</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>56150</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53684</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>53088</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>63374</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>59173</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,8%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>182</t>
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115590</t>
+          <t>115476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121245</t>
+          <t>121253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7711,107 +7711,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>604</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3022</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3605</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7824,74 +7824,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103343</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100571</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>100370</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>317</t>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210625</t>
+          <t>211208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8510,47 +8510,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8853,47 +8853,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9539,47 +9539,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9769,107 +9769,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3217</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2946</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -9882,72 +9882,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170261</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>167416</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170261</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>167884</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332079</t>
+          <t>331808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,74 +10112,74 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6377</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1824</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5521</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5523</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5588</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>743168</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>738467</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>702547</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>698850</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>703788</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>698848</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>703789</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>743168</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>739256</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2121</t>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1440989</t>
+          <t>1441344</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1448022</t>
+          <t>1447991</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
